--- a/Calibration_2.loop/Calibration cube measured X Y Z size.xlsx
+++ b/Calibration_2.loop/Calibration cube measured X Y Z size.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B677CC3-251B-479C-8250-030ADA437FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3764A603-28EB-4C69-8824-0A8778E0182D}"/>
+    <workbookView xWindow="14124" yWindow="0" windowWidth="9012" windowHeight="12336" xr2:uid="{3764A603-28EB-4C69-8824-0A8778E0182D}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration cube" sheetId="1" r:id="rId1"/>
